--- a/artfynd/A 6639-2024 artfynd.xlsx
+++ b/artfynd/A 6639-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>70316465</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800359.3620949021</v>
+        <v>800359</v>
       </c>
       <c r="R2" t="n">
-        <v>7310253.97592898</v>
+        <v>7310254</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -758,19 +753,9 @@
           <t>2018-04-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-04-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,60 +782,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70316470</v>
+        <v>70316479</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800359.3620949021</v>
+        <v>800359</v>
       </c>
       <c r="R3" t="n">
-        <v>7310253.97592898</v>
+        <v>7310254</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -880,19 +857,9 @@
           <t>2018-04-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-04-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +868,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6639-2024 artfynd.xlsx
+++ b/artfynd/A 6639-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70316465</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,8 +893,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70316479</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>